--- a/results/final_0624_summary/GpositivePseAAC_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/GpositivePseAAC_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.6268±0.0392</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5598±0.0545</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.4273±0.0424</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.3130±0.0324</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.7543±0.0258</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.8492±0.0268</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.9214±0.0238</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.9523±0.0176</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.6629±0.0354</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.6363±0.0447</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5485±0.0356</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.4580±0.0289</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.7514±0.0302</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.6770±0.0523</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5344±0.0462</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.3919±0.0383</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6253±0.0391</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5587±0.0545</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.4271±0.0425</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.3128±0.0322</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.5237±0.0344</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5104±0.0314</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.4546±0.0237</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.4063±0.0124</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4890±0.0392</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4139±0.0329</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.3302±0.0224</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.2793±0.0125</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6439±0.0574</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.7904±0.0634</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.9016±0.0358</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.9314±0.0327</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.4039±0.1084</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.4805±0.1271</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.6497±0.0719</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.8581±0.0477</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6053±0.0353</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5723±0.0409</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5005±0.0262</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.4415±0.0183</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5065±0.0392</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.4331±0.0441</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.3440±0.0242</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.2876±0.0151</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7535±0.0263</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.8490±0.0261</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9216±0.0245</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9521±0.0178</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.5298±0.0456</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.3748±0.0747</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.1666±0.0540</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0299±0.0332</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.6261±0.0383</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.5592±0.0533</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.4276±0.0429</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.3130±0.0312</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7582±0.0258</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.8502±0.0263</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.9224±0.0237</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.9533±0.0173</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.6635±0.0351</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.6360±0.0439</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.5490±0.0364</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.4583±0.0277</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.7499±0.0306</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6761±0.0514</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.5349±0.0472</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.3919±0.0369</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6247±0.0380</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5581±0.0533</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.4274±0.0431</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.3128±0.0310</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.5231±0.0348</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.5096±0.0312</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.4550±0.0246</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.4064±0.0117</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.4845±0.0389</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.4127±0.0321</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.3304±0.0228</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.2793±0.0118</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6470±0.0620</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7910±0.0635</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.9027±0.0367</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.9322±0.0330</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.4039±0.1084</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.4845±0.1239</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.6477±0.0757</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.8596±0.0485</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6051±0.0363</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.5717±0.0401</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.5011±0.0273</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.4417±0.0175</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.5045±0.0397</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.4321±0.0429</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.3444±0.0251</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.2877±0.0145</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7572±0.0258</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.8499±0.0255</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9226±0.0243</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9531±0.0175</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.5259±0.0421</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.3738±0.0729</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.1666±0.0540</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0289±0.0322</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.6274±0.0385</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.5593±0.0544</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.4270±0.0418</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.3130±0.0324</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.7562±0.0245</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.8482±0.0288</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.9205±0.0243</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.9523±0.0176</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.6638±0.0344</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.6356±0.0449</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.5480±0.0347</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.4580±0.0289</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.7514±0.0302</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.6763±0.0523</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.5339±0.0453</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.3919±0.0383</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6260±0.0384</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5582±0.0545</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.4268±0.0419</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.3128±0.0322</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.5243±0.0338</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5098±0.0321</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.4540±0.0227</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.4063±0.0124</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.4890±0.0391</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.4135±0.0333</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.3298±0.0215</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.2793±0.0125</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.6452±0.0577</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.7898±0.0641</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.9009±0.0354</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.9314±0.0327</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.4006±0.1103</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.4822±0.1262</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.6497±0.0719</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.8581±0.0477</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.6060±0.0348</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5714±0.0412</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.4999±0.0252</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.4415±0.0183</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5066±0.0392</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.4323±0.0442</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.3436±0.0234</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.2876±0.0151</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.7554±0.0251</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.8480±0.0279</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9206±0.0250</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9521±0.0178</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.5298±0.0456</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.3748±0.0747</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.1666±0.0540</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0299±0.0332</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.6255±0.0369</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.5590±0.0533</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.4276±0.0429</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.3130±0.0312</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.7601±0.0249</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.8502±0.0263</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.9224±0.0237</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.9533±0.0173</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.6635±0.0338</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.6358±0.0439</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.5490±0.0364</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.4583±0.0277</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.7490±0.0300</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.6756±0.0514</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.5349±0.0472</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.3919±0.0369</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.6240±0.0367</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5579±0.0533</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.4274±0.0431</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.3128±0.0310</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.5231±0.0338</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.5094±0.0315</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.4550±0.0246</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.4064±0.0117</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.4831±0.0371</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.4125±0.0323</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.3304±0.0228</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.2793±0.0118</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.6483±0.0625</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.7910±0.0635</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.9027±0.0367</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.9322±0.0330</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.4006±0.1103</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.4861±0.1232</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.6477±0.0757</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.8596±0.0485</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.6048±0.0352</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.5714±0.0403</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.5011±0.0273</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.4417±0.0175</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.5031±0.0386</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.4316±0.0430</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.3444±0.0251</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.2877±0.0145</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.7591±0.0250</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.8499±0.0255</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9226±0.0243</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9531±0.0175</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.5240±0.0413</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.3738±0.0729</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.1666±0.0540</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0289±0.0322</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.6340±0.0329</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.6173±0.0467</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.5757±0.0391</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.4961±0.0515</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.7543±0.0238</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.7692±0.0282</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.8241±0.0340</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.8088±0.0370</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.6685±0.0292</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.6595±0.0381</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.6446±0.0281</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.5843±0.0450</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.7586±0.0251</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.7386±0.0394</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.7078±0.0356</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.6506±0.0439</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6326±0.0328</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.6147±0.0457</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5746±0.0388</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.4945±0.0507</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.5299±0.0300</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.5157±0.0308</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.5109±0.0293</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.4633±0.0282</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.5003±0.0351</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.4682±0.0293</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.4269±0.0342</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.3656±0.0295</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.6440±0.0552</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.6573±0.0558</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.7195±0.0486</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.7206±0.0775</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.3905±0.1204</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.4662±0.1235</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.4617±0.1141</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.5237±0.0845</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.6121±0.0291</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.5986±0.0397</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.5883±0.0278</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.5390±0.0366</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.5160±0.0339</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.4922±0.0479</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.4590±0.0359</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.4058±0.0369</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.7535±0.0247</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.7677±0.0286</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.8241±0.0336</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8059±0.0371</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.5394±0.0413</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.5009±0.0665</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.4017±0.0669</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.2670±0.0650</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.6380±0.0307</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.6184±0.0428</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.5636±0.0322</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.4753±0.0442</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.7601±0.0197</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.7827±0.0174</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8309±0.0320</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.8334±0.0290</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.6732±0.0268</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.6639±0.0329</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.6390±0.0238</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.5765±0.0389</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.7630±0.0253</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.7393±0.0361</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.7028±0.0301</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.6340±0.0412</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.6366±0.0302</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.6157±0.0417</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.5625±0.0313</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.4736±0.0434</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.5352±0.0292</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.5191±0.0277</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.5048±0.0268</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.4595±0.0262</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.5044±0.0336</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.4644±0.0283</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.4164±0.0275</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.3529±0.0230</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.6500±0.0549</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.6690±0.0505</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.7081±0.0628</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.7376±0.0761</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.3980±0.1187</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.4735±0.1244</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.5047±0.1357</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.5643±0.0640</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.6182±0.0294</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.6033±0.0349</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.5857±0.0229</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.5347±0.0344</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.5220±0.0346</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.4928±0.0439</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.4533±0.0287</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.3947±0.0325</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.7592±0.0203</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.7811±0.0180</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8308±0.0321</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8308±0.0290</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.5413±0.0379</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.4942±0.0642</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.3699±0.0516</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.2139±0.0570</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.6372±0.0318</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.6171±0.0454</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.5764±0.0382</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.4979±0.0499</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.7524±0.0203</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.7693±0.0269</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.8232±0.0333</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.8054±0.0339</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.6701±0.0273</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.6591±0.0363</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.6447±0.0272</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.5847±0.0433</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.7601±0.0236</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.7372±0.0375</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.7083±0.0360</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.6518±0.0446</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.6358±0.0315</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.6144±0.0443</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5753±0.0381</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.4964±0.0495</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.5285±0.0269</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.5153±0.0275</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.5117±0.0285</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.4638±0.0274</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.4988±0.0328</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.4683±0.0265</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.4282±0.0328</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.3669±0.0290</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.6419±0.0525</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.6569±0.0554</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.7189±0.0480</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.7182±0.0758</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.4007±0.1203</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.4642±0.1231</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.4560±0.1168</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.5058±0.0904</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.6128±0.0265</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.5971±0.0368</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.5885±0.0279</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.5391±0.0370</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.5181±0.0322</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.4902±0.0456</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.4596±0.0365</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.4066±0.0377</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.7515±0.0213</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.7677±0.0273</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.8231±0.0330</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8030±0.0346</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.5471±0.0415</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.5019±0.0660</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.4036±0.0663</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.2718±0.0652</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.6395±0.0292</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.6196±0.0440</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.5626±0.0308</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.4737±0.0463</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7620±0.0138</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7818±0.0185</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.8299±0.0313</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.8339±0.0295</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.6746±0.0240</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.6647±0.0338</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.6377±0.0224</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.5753±0.0415</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.7630±0.0248</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.7398±0.0373</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.7011±0.0296</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.6333±0.0434</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6380±0.0287</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.6169±0.0426</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.5615±0.0300</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.4721±0.0457</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.5344±0.0263</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.5193±0.0268</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.5037±0.0266</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.4585±0.0271</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.5013±0.0343</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.4651±0.0263</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.4142±0.0271</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.3523±0.0238</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.6507±0.0502</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.6684±0.0507</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.7126±0.0656</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.7337±0.0747</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.3973±0.1234</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.4686±0.1289</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.5011±0.1313</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.5573±0.0624</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.6189±0.0267</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.6035±0.0358</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.5840±0.0222</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.5347±0.0369</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.5222±0.0341</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.4936±0.0451</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.4516±0.0282</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.3944±0.0345</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.7611±0.0147</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.7801±0.0190</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8298±0.0315</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8317±0.0300</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.5433±0.0385</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.4961±0.0650</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.3699±0.0503</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.2120±0.0574</t>
         </is>
@@ -1419,80 +3039,260 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.5183±0.0677</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.5366±0.0539</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.5317±0.0429</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.4764±0.0542</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.5163±0.0676</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.5390±0.0556</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.5379±0.0448</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.5092±0.0625</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.5170±0.0676</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.5369±0.0542</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.5330±0.0435</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.4862±0.0565</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.8560±0.0160</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.8528±0.0124</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.8466±0.0136</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.8107±0.0173</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.5163±0.0676</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.5351±0.0532</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.5293±0.0435</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.4740±0.0546</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.4431±0.0401</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.4573±0.0365</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.4675±0.0328</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.4407±0.0567</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.6262±0.0394</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.6191±0.0390</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.5959±0.0255</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.5373±0.0835</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.3669±0.0480</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.3875±0.0450</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.3973±0.0362</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.3897±0.0556</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>0.9960±0.0049</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>0.9184±0.1043</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.6402±0.0570</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.6459±0.0405</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.6370±0.0391</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.5731±0.0491</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.8552±0.0160</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.8194±0.0384</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.7869±0.0327</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.6643±0.0506</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.5143±0.0673</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.5363±0.0559</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.5364±0.0452</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.5076±0.0616</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.5144±0.0675</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.5298±0.0503</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.5182±0.0441</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.4383±0.0537</t>
         </is>
@@ -1526,80 +3326,260 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0.5646±0.0498</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.5173±0.0351</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.5137±0.0716</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.4903±0.0552</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.5626±0.0490</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.5173±0.0342</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.5206±0.0703</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.5211±0.0645</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>0.5633±0.0493</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.5170±0.0344</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.5158±0.0707</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.4998±0.0578</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.8569±0.0108</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.8504±0.0096</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.8441±0.0182</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.8148±0.0120</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.5626±0.0490</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.5163±0.0340</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.5132±0.0708</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.4884±0.0549</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.4676±0.0303</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.4448±0.0243</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.4478±0.0428</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.4444±0.0561</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.6246±0.0275</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.6183±0.0400</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.6022±0.0391</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.5349±0.0720</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.4034±0.0363</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.3703±0.0252</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.3776±0.0544</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.3990±0.0601</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>0.9970±0.0046</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.9308±0.1323</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.6624±0.0367</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.6335±0.0274</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.6234±0.0570</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.5838±0.0423</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.8140±0.0157</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.8278±0.0349</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.7926±0.0386</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.6726±0.0313</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.5601±0.0482</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.5142±0.0340</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.5173±0.0718</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.5200±0.0646</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.5607±0.0484</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.5144±0.0329</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.5056±0.0718</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.4547±0.0486</t>
         </is>
@@ -1653,62 +3633,1103 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>0.0270±0.0154</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0857±0.0299</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0520±0.0417</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0433±0.0399</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.0270±0.0154</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0857±0.0299</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0520±0.0417</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.0433±0.0399</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>0.7548±0.0048</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.7695±0.0081</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.7608±0.0117</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.7584±0.0111</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.0270±0.0154</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.0857±0.0299</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.0520±0.0417</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.0433±0.0399</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.0380±0.0225</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.1009±0.0267</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.0656±0.0477</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.0560±0.0510</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.2500±0.0000</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.2750±0.0750</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.2625±0.1625</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.2667±0.1658</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.0212±0.0133</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.0644±0.0218</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0401±0.0319</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.0342±0.0349</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.0518±0.0292</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.1555±0.0503</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.0955±0.0735</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.0798±0.0709</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.7833±0.3948</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.7639±0.3895</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.0268±0.0154</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.0851±0.0298</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.0518±0.0418</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.0432±0.0400</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0.0270±0.0154</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.0857±0.0299</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.0520±0.0417</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.0433±0.0399</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.5777±0.0475</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.5887±0.0600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.5886±0.0392</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.5711±0.0428</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.5606±0.0746</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.5462±0.0796</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.5399±0.0560</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.5173±0.0792</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.5587±0.0741</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.5443±0.0789</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.5447±0.0563</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.5342±0.0835</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.5593±0.0743</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.5449±0.0791</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.5412±0.0556</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.5223±0.0802</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.8584±0.0198</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.8535±0.0171</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.8485±0.0136</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.8312±0.0177</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.5587±0.0741</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.5443±0.0789</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.5388±0.0547</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.5159±0.0787</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.4492±0.0501</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.4421±0.0495</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.4385±0.0349</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.4389±0.0437</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.6315±0.0463</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.6238±0.0499</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.6093±0.0598</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.5609±0.0306</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.3937±0.0526</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.3847±0.0557</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.3845±0.0405</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.3915±0.0592</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.9931±0.0109</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.6618±0.0615</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.6477±0.0598</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.6418±0.0409</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.6103±0.0544</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.8225±0.0321</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.8172±0.0373</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.7952±0.0508</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.7295±0.0498</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.5562±0.0733</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.5418±0.0778</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.5419±0.0560</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.5315±0.0835</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.5568±0.0737</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.5424±0.0782</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.5317±0.0529</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.4971±0.0760</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.5008±0.0512</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.4949±0.0820</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.5243±0.0672</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.4285±0.0683</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.7167±0.0364</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.6974±0.0495</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.6382±0.0527</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.4646±0.0859</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.7138±0.0378</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.6950±0.0493</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.6430±0.0523</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.5406±0.0771</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.7148±0.0373</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.6958±0.0493</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.6390±0.0525</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.4895±0.0819</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.8564±0.0194</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.8468±0.0253</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.8321±0.0233</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.7618±0.0300</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.7138±0.0378</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.6950±0.0493</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.6358±0.0527</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.4636±0.0868</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.5285±0.0324</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.5249±0.0785</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.4767±0.0433</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.4061±0.0561</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.5607±0.0230</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.5832±0.1287</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.5302±0.0387</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.4143±0.0479</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.5303±0.0348</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.5214±0.0652</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.4701±0.0447</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.4274±0.0837</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.9500±0.1000</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.9970±0.0063</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.8573±0.1749</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.7140±0.0380</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.6948±0.0501</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.6579±0.0475</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.5316±0.0587</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.7167±0.0364</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.6974±0.0495</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.6764±0.0482</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.5279±0.0573</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.7114±0.0398</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.6922±0.0509</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.6415±0.0529</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.5384±0.0745</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.7109±0.0396</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.6926±0.0495</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.6262±0.0542</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.3873±0.1063</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.4813±0.0561</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.4560±0.0661</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.4354±0.1030</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.3804±0.0856</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.6068±0.0595</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.5818±0.0518</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.5101±0.0800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.4200±0.0524</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.6039±0.0587</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.5914±0.0512</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.5637±0.0926</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.5370±0.0615</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.6049±0.0589</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.5841±0.0511</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.5269±0.0827</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.4561±0.0495</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.8521±0.0125</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.8396±0.0113</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.8066±0.0195</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.7382±0.0457</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.6039±0.0587</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.5789±0.0506</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.5081±0.0788</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.4196±0.0516</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.5162±0.0465</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.5182±0.0599</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.4892±0.0841</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.4103±0.0361</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.6354±0.1080</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.6347±0.1050</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.5451±0.0725</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.4160±0.0400</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.4665±0.0508</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.4722±0.0590</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.4690±0.1028</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.4541±0.0566</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>0.9647±0.0658</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>0.8995±0.1554</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.8045±0.2108</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.7456±0.1501</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.6709±0.0377</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.6483±0.0341</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.5900±0.0618</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.5088±0.0453</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.7625±0.0279</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.7232±0.0265</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.6353±0.0522</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.4951±0.0701</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.6022±0.0593</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.5898±0.0516</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.5608±0.0904</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.5346±0.0634</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.6010±0.0581</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.5635±0.0499</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4529±0.0741</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.3179±0.0729</t>
         </is>
       </c>
     </row>
